--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N30_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N30_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>14.40843349440686</v>
+        <v>2.341370442841116</v>
       </c>
       <c r="D2" t="n">
-        <v>14.66536513996776</v>
+        <v>2.383121835244761</v>
       </c>
       <c r="E2" t="n">
-        <v>8.318833927908679</v>
+        <v>1.351810513285161</v>
       </c>
       <c r="F2" t="n">
-        <v>8.190770586925927</v>
+        <v>1.331000220375463</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.70584145467634</v>
+        <v>4.502199236384905</v>
       </c>
       <c r="D3" t="n">
-        <v>27.91117509058945</v>
+        <v>4.535565952220786</v>
       </c>
       <c r="E3" t="n">
-        <v>8.318833927908679</v>
+        <v>1.351810513285161</v>
       </c>
       <c r="F3" t="n">
-        <v>8.190770586925927</v>
+        <v>1.331000220375463</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>10.44081200513233</v>
+        <v>1.696631950834004</v>
       </c>
       <c r="D4" t="n">
-        <v>10.53271430893822</v>
+        <v>1.71156607520246</v>
       </c>
       <c r="E4" t="n">
-        <v>8.318833927908679</v>
+        <v>1.351810513285161</v>
       </c>
       <c r="F4" t="n">
-        <v>8.190770586925927</v>
+        <v>1.331000220375463</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.64406467364515</v>
+        <v>3.679660509467338</v>
       </c>
       <c r="D5" t="n">
-        <v>21.76131583453358</v>
+        <v>3.536213823111706</v>
       </c>
       <c r="E5" t="n">
-        <v>8.318833927908679</v>
+        <v>1.351810513285161</v>
       </c>
       <c r="F5" t="n">
-        <v>8.190770586925927</v>
+        <v>1.331000220375463</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>24.44616746154829</v>
+        <v>3.972502212501597</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>1.1375</v>
       </c>
       <c r="E6" t="n">
-        <v>8.318833927908679</v>
+        <v>1.351810513285161</v>
       </c>
       <c r="F6" t="n">
-        <v>8.190770586925927</v>
+        <v>1.331000220375463</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>14.37542254877775</v>
+        <v>2.336006164176384</v>
       </c>
       <c r="D7" t="n">
-        <v>14.19523838529315</v>
+        <v>2.306726237610137</v>
       </c>
       <c r="E7" t="n">
-        <v>8.318833927908679</v>
+        <v>1.351810513285161</v>
       </c>
       <c r="F7" t="n">
-        <v>8.190770586925927</v>
+        <v>1.331000220375463</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>22.59786400232392</v>
+        <v>3.672152900377637</v>
       </c>
       <c r="D8" t="n">
-        <v>22.55004639572285</v>
+        <v>3.664382539304963</v>
       </c>
       <c r="E8" t="n">
-        <v>8.318833927908679</v>
+        <v>1.351810513285161</v>
       </c>
       <c r="F8" t="n">
-        <v>8.190770586925927</v>
+        <v>1.331000220375463</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>15.29352322158813</v>
+        <v>2.485197523508071</v>
       </c>
       <c r="D9" t="n">
-        <v>15.94205648514867</v>
+        <v>2.590584178836658</v>
       </c>
       <c r="E9" t="n">
-        <v>8.318833927908679</v>
+        <v>1.351810513285161</v>
       </c>
       <c r="F9" t="n">
-        <v>8.190770586925927</v>
+        <v>1.331000220375463</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>21.42739726508178</v>
+        <v>3.48195205557579</v>
       </c>
       <c r="D10" t="n">
-        <v>16.28413997926132</v>
+        <v>2.646172746629964</v>
       </c>
       <c r="E10" t="n">
-        <v>8.318833927908679</v>
+        <v>1.351810513285161</v>
       </c>
       <c r="F10" t="n">
-        <v>8.190770586925927</v>
+        <v>1.331000220375463</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>37.3676514922814</v>
+        <v>6.072243367495727</v>
       </c>
       <c r="D11" t="n">
-        <v>25.30316185775999</v>
+        <v>4.111763801885998</v>
       </c>
       <c r="E11" t="n">
-        <v>8.318833927908679</v>
+        <v>1.351810513285161</v>
       </c>
       <c r="F11" t="n">
-        <v>8.190770586925927</v>
+        <v>1.331000220375463</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>32.1933760403758</v>
+        <v>5.231423606561068</v>
       </c>
       <c r="D12" t="n">
-        <v>32.60688593956171</v>
+        <v>5.298618965178779</v>
       </c>
       <c r="E12" t="n">
-        <v>8.318833927908679</v>
+        <v>1.351810513285161</v>
       </c>
       <c r="F12" t="n">
-        <v>8.190770586925927</v>
+        <v>1.331000220375463</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>22.13887722994316</v>
+        <v>3.597567549865763</v>
       </c>
       <c r="D13" t="n">
-        <v>25.05992817228334</v>
+        <v>4.072238327996042</v>
       </c>
       <c r="E13" t="n">
-        <v>8.318833927908679</v>
+        <v>1.351810513285161</v>
       </c>
       <c r="F13" t="n">
-        <v>8.190770586925927</v>
+        <v>1.331000220375463</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>20.86377734415297</v>
+        <v>3.390363818424858</v>
       </c>
       <c r="D14" t="n">
-        <v>24.46709610607281</v>
+        <v>3.975903117236832</v>
       </c>
       <c r="E14" t="n">
-        <v>8.318833927908679</v>
+        <v>1.351810513285161</v>
       </c>
       <c r="F14" t="n">
-        <v>8.190770586925927</v>
+        <v>1.331000220375463</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>29.44895184852988</v>
+        <v>4.785454675386107</v>
       </c>
       <c r="D15" t="n">
-        <v>32.9164443758872</v>
+        <v>5.348922211081669</v>
       </c>
       <c r="E15" t="n">
-        <v>8.318833927908679</v>
+        <v>1.351810513285161</v>
       </c>
       <c r="F15" t="n">
-        <v>8.190770586925927</v>
+        <v>1.331000220375463</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>15.01720856727488</v>
+        <v>2.440296392182168</v>
       </c>
       <c r="D16" t="n">
-        <v>15.47707412251199</v>
+        <v>2.515024544908199</v>
       </c>
       <c r="E16" t="n">
-        <v>8.318833927908679</v>
+        <v>1.351810513285161</v>
       </c>
       <c r="F16" t="n">
-        <v>8.190770586925927</v>
+        <v>1.331000220375463</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>39.09907179788975</v>
+        <v>6.353599167157085</v>
       </c>
       <c r="D17" t="n">
-        <v>13.06847588117536</v>
+        <v>2.123627330690996</v>
       </c>
       <c r="E17" t="n">
-        <v>8.318833927908679</v>
+        <v>1.351810513285161</v>
       </c>
       <c r="F17" t="n">
-        <v>8.190770586925927</v>
+        <v>1.331000220375463</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>34.54777870631276</v>
+        <v>5.614014039775823</v>
       </c>
       <c r="D18" t="n">
-        <v>3.708292289522543</v>
+        <v>0.6025974970474132</v>
       </c>
       <c r="E18" t="n">
-        <v>8.318833927908679</v>
+        <v>1.351810513285161</v>
       </c>
       <c r="F18" t="n">
-        <v>8.190770586925927</v>
+        <v>1.331000220375463</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
